--- a/EX1/CP_res/EX1_CPa_effectivenes_all models.xlsx
+++ b/EX1/CP_res/EX1_CPa_effectivenes_all models.xlsx
@@ -1,65 +1,82 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xhulj\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2847C6DD-99B5-4AD3-890F-BFF69D8AA68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="16080" windowWidth="29040" windowHeight="7965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="LApredict" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="DeepJIT" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="CodeBERT4JIT" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="LApredict" sheetId="1" r:id="rId1"/>
+    <sheet name="DeepJIT" sheetId="2" r:id="rId2"/>
+    <sheet name="CodeBERT4JIT" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
-  <si>
-    <t xml:space="preserve">Correct predictions made by Lapredict</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Predictions with prob. &gt; alpha</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="55">
+  <si>
+    <t>Correct predictions made by Lapredict</t>
+  </si>
+  <si>
+    <t>Predictions with prob. &gt; alpha</t>
   </si>
   <si>
     <t>Alpha</t>
   </si>
   <si>
-    <t xml:space="preserve">Data subset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Rows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tot. Correct Predictions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tot. Correct Clean Predictions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tot. Correct Fault-prone Predictions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nr. flagged predictions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nr. flagged Clean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nr. flagged Fault-prone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nr. correctly flagged predictions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nr. correctly flagged Clean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nr. correctly flagged Fault-prone</t>
+    <t>Data subset</t>
+  </si>
+  <si>
+    <t>Total Rows</t>
+  </si>
+  <si>
+    <t>Tot. Correct Predictions</t>
+  </si>
+  <si>
+    <t>Tot. Correct Clean Predictions</t>
+  </si>
+  <si>
+    <t>Tot. Correct Fault-prone Predictions</t>
+  </si>
+  <si>
+    <t>Nr. flagged predictions</t>
+  </si>
+  <si>
+    <t>Nr. flagged Clean</t>
+  </si>
+  <si>
+    <t>Nr. flagged Fault-prone</t>
+  </si>
+  <si>
+    <t>Nr. correctly flagged predictions</t>
+  </si>
+  <si>
+    <t>Nr. correctly flagged Clean</t>
+  </si>
+  <si>
+    <t>Nr. correctly flagged Fault-prone</t>
   </si>
   <si>
     <t>Precision</t>
@@ -77,7 +94,7 @@
     <t>Recall-clean</t>
   </si>
   <si>
-    <t xml:space="preserve">Recall Fault-prone</t>
+    <t>Recall Fault-prone</t>
   </si>
   <si>
     <t xml:space="preserve">OPENSTACK </t>
@@ -86,7 +103,7 @@
     <t>0.95</t>
   </si>
   <si>
-    <t xml:space="preserve">Test avg</t>
+    <t>Test avg</t>
   </si>
   <si>
     <t>0.91</t>
@@ -98,7 +115,7 @@
     <t>0.9</t>
   </si>
   <si>
-    <t xml:space="preserve">Test AVG</t>
+    <t>Test AVG</t>
   </si>
   <si>
     <t>0.89</t>
@@ -131,10 +148,10 @@
     <t>0.99</t>
   </si>
   <si>
-    <t xml:space="preserve">LApredict with Openstack makes 3707 correct predictions; 3506 clean and 201 fault-prone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LApredict with QT makes 4088 correct predictions; 4063 clean and 25 fault-prone</t>
+    <t>LApredict with Openstack makes 3707 correct predictions; 3506 clean and 201 fault-prone</t>
+  </si>
+  <si>
+    <t>LApredict with QT makes 4088 correct predictions; 4063 clean and 25 fault-prone</t>
   </si>
   <si>
     <t>0.77</t>
@@ -161,10 +178,10 @@
     <t>0.78</t>
   </si>
   <si>
-    <t xml:space="preserve">DeepJIT with Openstack makes 777 correct predictions; 639 clean and 138 fault-prone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DeepJIT with QT makes 1851 correct predictions; 1727 clean and 124 fault-prone</t>
+    <t>DeepJIT with Openstack makes 777 correct predictions; 639 clean and 138 fault-prone</t>
+  </si>
+  <si>
+    <t>DeepJIT with QT makes 1851 correct predictions; 1727 clean and 124 fault-prone</t>
   </si>
   <si>
     <t>0.93</t>
@@ -179,58 +196,58 @@
     <t>0.94</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeBERT4JIT with openstack makes 1144 correct predictions, where 1111 are clean and 33 fault prone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeBERT4JIT with QT makes 2355 correct predictions; 2326  clean, 29 fault-prone</t>
+    <t>CodeBERT4JIT with openstack makes 1144 correct predictions, where 1111 are clean and 33 fault prone</t>
+  </si>
+  <si>
+    <t>CodeBERT4JIT with QT makes 2355 correct predictions; 2326  clean, 29 fault-prone</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="9"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="9"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="8" tint="0.39997558519241921"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color rgb="FF7030A0"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="8" tint="-0.249977111117893"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
@@ -264,20 +281,20 @@
   </fills>
   <borders count="4">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -292,7 +309,7 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -301,80 +318,77 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="25">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="1" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf fontId="2" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf fontId="3" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf fontId="2" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf fontId="2" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf fontId="2" fillId="4" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="7" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="7" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf fontId="2" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf fontId="2" fillId="4" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -393,291 +407,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -888,113 +619,115 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="8.88671875"/>
-    <col customWidth="1" min="4" max="6" width="16"/>
-    <col customWidth="1" min="7" max="7" style="1" width="15.44140625"/>
-    <col customWidth="1" min="8" max="9" width="11"/>
-    <col customWidth="1" min="10" max="10" style="1" width="15.88671875"/>
-    <col customWidth="1" min="11" max="12" width="15.88671875"/>
-    <col customWidth="1" min="13" max="13" width="9.75390625"/>
-    <col customWidth="1" min="14" max="15" width="11.625"/>
-    <col customWidth="1" min="16" max="16" width="12.44140625"/>
+    <col min="3" max="3" width="8.88671875" customWidth="1"/>
+    <col min="4" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="15.44140625" style="1" customWidth="1"/>
+    <col min="8" max="9" width="11" customWidth="1"/>
+    <col min="10" max="10" width="15.88671875" style="1" customWidth="1"/>
+    <col min="11" max="12" width="15.88671875" customWidth="1"/>
+    <col min="13" max="13" width="9.77734375" customWidth="1"/>
+    <col min="14" max="15" width="11.6640625" customWidth="1"/>
+    <col min="16" max="16" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="D1" s="2" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="D1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="3" t="s">
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-    </row>
-    <row r="2" ht="28.050000000000001" customHeight="1">
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+    </row>
+    <row r="2" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="11" t="s">
+      <c r="P2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="12" t="s">
+      <c r="Q2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="12" t="s">
+      <c r="R2" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" ht="25.949999999999999" customHeight="1">
-      <c r="A4" s="13" t="s">
+    <row r="4" spans="1:18" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-    </row>
-    <row r="5">
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1007,6 +740,12 @@
       <c r="D5">
         <v>3707</v>
       </c>
+      <c r="E5">
+        <v>3506</v>
+      </c>
+      <c r="F5">
+        <v>201</v>
+      </c>
       <c r="G5" s="1">
         <v>1812</v>
       </c>
@@ -1025,36 +764,36 @@
       <c r="L5">
         <v>33</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="M5" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="N5" s="16">
+      <c r="N5" s="11">
         <f>K5/H5</f>
         <v>0.99508901166359731</v>
       </c>
-      <c r="O5" s="16">
+      <c r="O5" s="11">
         <f>L5/I5</f>
         <v>0.18032786885245902</v>
       </c>
-      <c r="P5" s="15" t="s">
+      <c r="P5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="Q5" s="16">
+      <c r="Q5" s="11">
         <f>K5/3506</f>
         <v>0.46235025670279523</v>
       </c>
-      <c r="R5" s="16">
+      <c r="R5" s="11">
         <f>L5/201</f>
         <v>0.16417910447761194</v>
       </c>
     </row>
-    <row r="6">
-      <c r="M6" s="15"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="15"/>
-    </row>
-    <row r="7">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="M6" s="10"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="10"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1067,6 +806,12 @@
       <c r="D7">
         <v>3707</v>
       </c>
+      <c r="E7">
+        <v>3506</v>
+      </c>
+      <c r="F7">
+        <v>201</v>
+      </c>
       <c r="G7" s="1">
         <v>2772</v>
       </c>
@@ -1085,36 +830,36 @@
       <c r="L7">
         <v>52</v>
       </c>
-      <c r="M7" s="15" t="s">
+      <c r="M7" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="N7" s="17">
+      <c r="N7" s="11">
         <f>K7/H7</f>
         <v>0.99097250718096019</v>
       </c>
-      <c r="O7" s="17">
+      <c r="O7" s="11">
         <f>L7/I7</f>
         <v>0.15522388059701492</v>
       </c>
-      <c r="P7" s="15" t="s">
+      <c r="P7" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="Q7" s="16">
+      <c r="Q7" s="11">
         <f>K7/3506</f>
         <v>0.68881916714204217</v>
       </c>
-      <c r="R7" s="16">
+      <c r="R7" s="11">
         <f>L7/201</f>
         <v>0.25870646766169153</v>
       </c>
     </row>
-    <row r="8">
-      <c r="M8" s="15"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="15"/>
-    </row>
-    <row r="9">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="M8" s="10"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="10"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -1127,6 +872,12 @@
       <c r="D9">
         <v>3707</v>
       </c>
+      <c r="E9">
+        <v>3506</v>
+      </c>
+      <c r="F9">
+        <v>201</v>
+      </c>
       <c r="G9" s="1">
         <v>3528</v>
       </c>
@@ -1145,50 +896,50 @@
       <c r="L9">
         <v>92</v>
       </c>
-      <c r="M9" s="15" t="s">
+      <c r="M9" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="N9" s="17">
+      <c r="N9" s="11">
         <f>K9/H9</f>
         <v>0.98567144285238251</v>
       </c>
-      <c r="O9" s="17">
+      <c r="O9" s="11">
         <f>L9/I9</f>
         <v>0.17457305502846299</v>
       </c>
-      <c r="P9" s="15" t="s">
+      <c r="P9" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="Q9" s="16">
+      <c r="Q9" s="11">
         <f>K9/3506</f>
         <v>0.84369652025099828</v>
       </c>
-      <c r="R9" s="16">
+      <c r="R9" s="11">
         <f>L9/201</f>
         <v>0.45771144278606968</v>
       </c>
     </row>
-    <row r="12" ht="25.949999999999999" customHeight="1">
-      <c r="A12" s="13" t="s">
+    <row r="12" spans="1:18" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="13"/>
-    </row>
-    <row r="13">
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -1201,6 +952,12 @@
       <c r="D13">
         <v>4088</v>
       </c>
+      <c r="E13">
+        <v>4063</v>
+      </c>
+      <c r="F13">
+        <v>25</v>
+      </c>
       <c r="G13" s="1">
         <v>2706</v>
       </c>
@@ -1219,34 +976,34 @@
       <c r="L13">
         <v>1</v>
       </c>
-      <c r="M13" s="15" t="s">
+      <c r="M13" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="N13" s="17">
+      <c r="N13" s="11">
         <f>K13/H13</f>
         <v>0.999185667752443</v>
       </c>
-      <c r="O13" s="17">
+      <c r="O13" s="11">
         <f>L13/I13</f>
-        <v>0.0040000000000000001</v>
-      </c>
-      <c r="P13" s="15" t="s">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="P13" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="Q13" s="16">
+      <c r="Q13" s="11">
         <f>K13/4063</f>
         <v>0.6039872015751907</v>
       </c>
-      <c r="R13" s="16">
+      <c r="R13" s="11">
         <f>L13/25</f>
-        <v>0.040000000000000001</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="M14" s="15"/>
-      <c r="P14" s="15"/>
-    </row>
-    <row r="15">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="M14" s="10"/>
+      <c r="P14" s="10"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -1259,6 +1016,12 @@
       <c r="D15">
         <v>4088</v>
       </c>
+      <c r="E15">
+        <v>4063</v>
+      </c>
+      <c r="F15">
+        <v>25</v>
+      </c>
       <c r="G15" s="1">
         <v>4049</v>
       </c>
@@ -1277,34 +1040,34 @@
       <c r="L15">
         <v>5</v>
       </c>
-      <c r="M15" s="15" t="s">
+      <c r="M15" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="N15" s="17">
+      <c r="N15" s="11">
         <f>K15/H15</f>
         <v>0.99859471613265882</v>
       </c>
-      <c r="O15" s="17">
+      <c r="O15" s="11">
         <f>L15/I15</f>
-        <v>0.010183299389002037</v>
-      </c>
-      <c r="P15" s="15" t="s">
+        <v>1.0183299389002037E-2</v>
+      </c>
+      <c r="P15" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Q15" s="16">
+      <c r="Q15" s="11">
         <f>K15/4063</f>
         <v>0.87447698744769875</v>
       </c>
-      <c r="R15" s="16">
+      <c r="R15" s="11">
         <f>L15/25</f>
-        <v>0.20000000000000001</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="M16" s="15"/>
-      <c r="P16" s="15"/>
-    </row>
-    <row r="17">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="M16" s="10"/>
+      <c r="P16" s="10"/>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -1317,6 +1080,12 @@
       <c r="D17">
         <v>4088</v>
       </c>
+      <c r="E17">
+        <v>4063</v>
+      </c>
+      <c r="F17">
+        <v>25</v>
+      </c>
       <c r="G17" s="1">
         <v>4698</v>
       </c>
@@ -1335,36 +1104,36 @@
       <c r="L17">
         <v>15</v>
       </c>
-      <c r="M17" s="15" t="s">
+      <c r="M17" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="N17" s="17">
+      <c r="N17" s="11">
         <f>K17/H17</f>
         <v>0.99702307119821387</v>
       </c>
-      <c r="O17" s="17">
+      <c r="O17" s="11">
         <f>L17/I17</f>
-        <v>0.022488755622188907</v>
-      </c>
-      <c r="P17" s="15" t="s">
+        <v>2.2488755622188907E-2</v>
+      </c>
+      <c r="P17" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Q17" s="16">
+      <c r="Q17" s="11">
         <f>K17/4063</f>
         <v>0.98917056362293876</v>
       </c>
-      <c r="R17" s="16">
+      <c r="R17" s="11">
         <f>L17/25</f>
-        <v>0.59999999999999998</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25">
-      <c r="A21" s="18" t="s">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A21" s="12" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" ht="14.25">
-      <c r="A22" s="18" t="s">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A22" s="12" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1375,125 +1144,124 @@
     <mergeCell ref="A4:P4"/>
     <mergeCell ref="A12:P12"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:R22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col customWidth="1" min="3" max="5" width="10.33203125"/>
-    <col customWidth="1" min="6" max="6" width="9.33203125"/>
-    <col customWidth="1" min="7" max="7" style="19" width="19.33203125"/>
-    <col customWidth="1" min="8" max="9" width="6.109375"/>
-    <col customWidth="1" min="10" max="10" style="1" width="12.33203125"/>
-    <col customWidth="1" min="11" max="12" width="8.77734375"/>
-    <col bestFit="1" customWidth="1" min="13" max="13" style="20" width="8.77734375"/>
-    <col customWidth="1" min="14" max="15" width="8.77734375"/>
-    <col bestFit="1" customWidth="1" min="16" max="16" style="20" width="8.77734375"/>
-    <col bestFit="1" customWidth="1" min="17" max="18" width="8.77734375"/>
+    <col min="3" max="5" width="10.33203125" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" customWidth="1"/>
+    <col min="7" max="7" width="19.33203125" style="13" customWidth="1"/>
+    <col min="8" max="9" width="6.109375" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="8.77734375" customWidth="1"/>
+    <col min="13" max="13" width="8.77734375" style="14" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="8.77734375" customWidth="1"/>
+    <col min="16" max="16" width="8.77734375" style="14" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="8.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="D1" s="2" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="D1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="3" t="s">
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
       <c r="M1"/>
       <c r="P1"/>
     </row>
-    <row r="2" ht="28.050000000000001" customHeight="1">
+    <row r="2" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="11" t="s">
+      <c r="P2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="12" t="s">
+      <c r="Q2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="12" t="s">
+      <c r="R2" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="G3" s="1"/>
       <c r="M3"/>
       <c r="P3"/>
     </row>
-    <row r="4" ht="25.949999999999999" customHeight="1">
-      <c r="A4" s="13" t="s">
+    <row r="4" spans="1:18" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-    </row>
-    <row r="5">
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1504,11 +1272,13 @@
         <v>1331</v>
       </c>
       <c r="D5">
-        <v>1168</v>
+        <v>777</v>
+      </c>
+      <c r="E5">
+        <v>639</v>
       </c>
       <c r="F5">
-        <f>G5/C5</f>
-        <v>0.2742299023290759</v>
+        <v>138</v>
       </c>
       <c r="G5" s="1">
         <v>365</v>
@@ -1528,40 +1298,40 @@
       <c r="L5">
         <v>25</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="M5" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="N5" s="16">
+      <c r="N5" s="11">
         <f>K5/H5</f>
         <v>0.77910447761194035</v>
       </c>
-      <c r="O5" s="16">
+      <c r="O5" s="11">
         <f>L5/I5</f>
         <v>0.86206896551724133</v>
       </c>
-      <c r="P5" s="15">
+      <c r="P5" s="10">
         <f>J5/777</f>
         <v>0.36808236808236811</v>
       </c>
-      <c r="Q5" s="16">
+      <c r="Q5" s="11">
         <f>K5/639</f>
         <v>0.40845070422535212</v>
       </c>
-      <c r="R5" s="17">
+      <c r="R5" s="11">
         <f>L5/138</f>
         <v>0.18115942028985507</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="G6" s="1"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
-    </row>
-    <row r="7">
+      <c r="M6" s="10"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1572,7 +1342,13 @@
         <v>1331</v>
       </c>
       <c r="D7">
-        <v>1168</v>
+        <v>777</v>
+      </c>
+      <c r="E7">
+        <v>639</v>
+      </c>
+      <c r="F7">
+        <v>138</v>
       </c>
       <c r="G7" s="1">
         <v>615</v>
@@ -1592,40 +1368,40 @@
       <c r="L7">
         <v>50</v>
       </c>
-      <c r="M7" s="15" t="s">
+      <c r="M7" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="N7" s="17">
+      <c r="N7" s="11">
         <f>K7/H7</f>
         <v>0.7571942446043165</v>
       </c>
-      <c r="O7" s="17">
+      <c r="O7" s="11">
         <f>L7/I7</f>
         <v>0.84745762711864403</v>
       </c>
-      <c r="P7" s="15">
+      <c r="P7" s="10">
         <f>J7/777</f>
         <v>0.60617760617760619</v>
       </c>
-      <c r="Q7" s="17">
+      <c r="Q7" s="11">
         <f>K7/639</f>
         <v>0.65884194053208134</v>
       </c>
-      <c r="R7" s="17">
+      <c r="R7" s="11">
         <f>L7/138</f>
         <v>0.36231884057971014</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="G8" s="1"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="16"/>
-    </row>
-    <row r="9">
+      <c r="M8" s="10"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -1636,7 +1412,13 @@
         <v>1331</v>
       </c>
       <c r="D9">
-        <v>1168</v>
+        <v>777</v>
+      </c>
+      <c r="E9">
+        <v>639</v>
+      </c>
+      <c r="F9">
+        <v>138</v>
       </c>
       <c r="G9" s="1">
         <v>730</v>
@@ -1656,61 +1438,61 @@
       <c r="L9">
         <v>72</v>
       </c>
-      <c r="M9" s="15" t="s">
+      <c r="M9" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="N9" s="17">
+      <c r="N9" s="11">
         <f>K9/H9</f>
         <v>0.67592592592592593</v>
       </c>
-      <c r="O9" s="17">
+      <c r="O9" s="11">
         <f>L9/I9</f>
         <v>0.87804878048780488</v>
       </c>
-      <c r="P9" s="15">
+      <c r="P9" s="10">
         <f>J9/777</f>
         <v>0.65765765765765771</v>
       </c>
-      <c r="Q9" s="17">
+      <c r="Q9" s="11">
         <f>K9/639</f>
         <v>0.68544600938967137</v>
       </c>
-      <c r="R9" s="17">
+      <c r="R9" s="11">
         <f>L9/138</f>
         <v>0.52173913043478259</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="G10" s="1"/>
       <c r="M10"/>
       <c r="P10"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="G11" s="1"/>
       <c r="M11"/>
       <c r="P11"/>
     </row>
-    <row r="12" ht="25.949999999999999" customHeight="1">
-      <c r="A12" s="13" t="s">
+    <row r="12" spans="1:18" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="13"/>
-    </row>
-    <row r="13">
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -1723,6 +1505,12 @@
       <c r="D13">
         <v>1851</v>
       </c>
+      <c r="E13">
+        <v>1727</v>
+      </c>
+      <c r="F13">
+        <v>124</v>
+      </c>
       <c r="G13" s="1">
         <v>691</v>
       </c>
@@ -1741,39 +1529,39 @@
       <c r="L13">
         <v>42</v>
       </c>
-      <c r="M13" s="15" t="s">
+      <c r="M13" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="N13" s="17">
+      <c r="N13" s="11">
         <f>K13/H13</f>
         <v>0.81464174454828664</v>
       </c>
-      <c r="O13" s="17">
+      <c r="O13" s="11">
         <f>L13/I13</f>
         <v>0.8571428571428571</v>
       </c>
-      <c r="P13" s="15" t="s">
+      <c r="P13" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="Q13" s="16">
+      <c r="Q13" s="11">
         <f>K13/1727</f>
         <v>0.30283729009843657</v>
       </c>
-      <c r="R13" s="16">
+      <c r="R13" s="11">
         <f>L13/124</f>
         <v>0.33870967741935482</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="G14" s="1"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-    </row>
-    <row r="15">
+      <c r="M14" s="10"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -1786,6 +1574,12 @@
       <c r="D15">
         <v>1851</v>
       </c>
+      <c r="E15">
+        <v>1727</v>
+      </c>
+      <c r="F15">
+        <v>124</v>
+      </c>
       <c r="G15" s="1">
         <v>1344</v>
       </c>
@@ -1804,39 +1598,39 @@
       <c r="L15">
         <v>72</v>
       </c>
-      <c r="M15" s="15" t="s">
+      <c r="M15" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="N15" s="17">
+      <c r="N15" s="11">
         <f>K15/H15</f>
         <v>0.80815347721822539</v>
       </c>
-      <c r="O15" s="17">
+      <c r="O15" s="11">
         <f>L15/I15</f>
         <v>0.77419354838709675</v>
       </c>
-      <c r="P15" s="15" t="s">
+      <c r="P15" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="Q15" s="17">
+      <c r="Q15" s="11">
         <f>K15/1727</f>
         <v>0.58540822235089751</v>
       </c>
-      <c r="R15" s="17">
+      <c r="R15" s="11">
         <f>L15/124</f>
         <v>0.58064516129032262</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="G16" s="1"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="16"/>
-    </row>
-    <row r="17">
+      <c r="M16" s="10"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -1849,6 +1643,12 @@
       <c r="D17">
         <v>1851</v>
       </c>
+      <c r="E17">
+        <v>1727</v>
+      </c>
+      <c r="F17">
+        <v>124</v>
+      </c>
       <c r="G17" s="1">
         <v>1810</v>
       </c>
@@ -1867,36 +1667,36 @@
       <c r="L17">
         <v>96</v>
       </c>
-      <c r="M17" s="15" t="s">
+      <c r="M17" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="N17" s="17">
+      <c r="N17" s="11">
         <f>K17/H17</f>
         <v>0.78115682766845562</v>
       </c>
-      <c r="O17" s="17">
+      <c r="O17" s="11">
         <f>L17/I17</f>
         <v>0.72180451127819545</v>
       </c>
-      <c r="P17" s="15" t="s">
+      <c r="P17" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="Q17" s="17">
+      <c r="Q17" s="11">
         <f>K17/1727</f>
         <v>0.75854082223508978</v>
       </c>
-      <c r="R17" s="17">
+      <c r="R17" s="11">
         <f>L17/124</f>
         <v>0.77419354838709675</v>
       </c>
     </row>
-    <row r="21" ht="14.4">
-      <c r="A21" s="18" t="s">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A21" s="12" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="22" ht="14.4">
-      <c r="A22" s="18" t="s">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A22" s="12" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1907,125 +1707,124 @@
     <mergeCell ref="A4:P4"/>
     <mergeCell ref="A12:P12"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:R22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col customWidth="1" min="3" max="6" width="8.88671875"/>
-    <col customWidth="1" min="7" max="7" style="19" width="20.6640625"/>
-    <col customWidth="1" min="8" max="9" width="8.88671875"/>
-    <col customWidth="1" min="10" max="10" style="19" width="16.77734375"/>
-    <col customWidth="1" min="11" max="12" width="8.88671875"/>
-    <col min="13" max="13" style="21" width="9"/>
-    <col customWidth="1" min="14" max="15" width="8.88671875"/>
-    <col min="16" max="16" style="21" width="9"/>
+    <col min="3" max="6" width="8.88671875" customWidth="1"/>
+    <col min="7" max="7" width="20.6640625" style="13" customWidth="1"/>
+    <col min="8" max="9" width="8.88671875" customWidth="1"/>
+    <col min="10" max="10" width="16.77734375" style="13" customWidth="1"/>
+    <col min="11" max="12" width="8.88671875" customWidth="1"/>
+    <col min="13" max="13" width="9" style="15"/>
+    <col min="14" max="15" width="8.88671875" customWidth="1"/>
+    <col min="16" max="16" width="9" style="15"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="D1" s="2" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="D1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="3" t="s">
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
       <c r="J1" s="1"/>
-      <c r="M1" s="22"/>
-      <c r="P1" s="22"/>
-    </row>
-    <row r="2" ht="28.050000000000001" customHeight="1">
+      <c r="M1" s="16"/>
+      <c r="P1" s="16"/>
+    </row>
+    <row r="2" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="23" t="s">
+      <c r="M2" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="24" t="s">
+      <c r="P2" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="12" t="s">
+      <c r="Q2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="12" t="s">
+      <c r="R2" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="G3" s="1"/>
       <c r="J3" s="1"/>
-      <c r="M3" s="22"/>
-      <c r="P3" s="22"/>
-    </row>
-    <row r="4" ht="25.949999999999999" customHeight="1">
-      <c r="A4" s="13" t="s">
+      <c r="M3" s="16"/>
+      <c r="P3" s="16"/>
+    </row>
+    <row r="4" spans="1:18" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-    </row>
-    <row r="5">
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -2038,6 +1837,12 @@
       <c r="D5">
         <v>1144</v>
       </c>
+      <c r="E5">
+        <v>1111</v>
+      </c>
+      <c r="F5">
+        <v>33</v>
+      </c>
       <c r="G5" s="1">
         <v>967</v>
       </c>
@@ -2056,40 +1861,40 @@
       <c r="L5">
         <v>3</v>
       </c>
-      <c r="M5" s="25" t="s">
+      <c r="M5" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="N5" s="16">
+      <c r="N5" s="11">
         <f>K5/H5</f>
         <v>0.99555555555555553</v>
       </c>
-      <c r="O5" s="16">
+      <c r="O5" s="11">
         <f>L5/I5</f>
-        <v>0.044776119402985072</v>
-      </c>
-      <c r="P5" s="25" t="s">
+        <v>4.4776119402985072E-2</v>
+      </c>
+      <c r="P5" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="Q5" s="16">
+      <c r="Q5" s="11">
         <f>K5/1111</f>
         <v>0.80648064806480646</v>
       </c>
-      <c r="R5" s="16">
+      <c r="R5" s="11">
         <f>L5/33</f>
-        <v>0.090909090909090912</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>9.0909090909090912E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="G6" s="1"/>
       <c r="J6" s="1"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="25"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
-    </row>
-    <row r="7">
+      <c r="M6" s="19"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -2102,6 +1907,12 @@
       <c r="D7">
         <v>1144</v>
       </c>
+      <c r="E7">
+        <v>1111</v>
+      </c>
+      <c r="F7">
+        <v>33</v>
+      </c>
       <c r="G7" s="1">
         <v>1227</v>
       </c>
@@ -2120,40 +1931,40 @@
       <c r="L7">
         <v>14</v>
       </c>
-      <c r="M7" s="25" t="s">
+      <c r="M7" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="N7" s="17">
+      <c r="N7" s="11">
         <f>K7/H7</f>
         <v>0.98085688240656332</v>
       </c>
-      <c r="O7" s="17">
+      <c r="O7" s="11">
         <f>L7/I7</f>
         <v>0.1076923076923077</v>
       </c>
-      <c r="P7" s="25" t="s">
+      <c r="P7" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="Q7" s="17">
+      <c r="Q7" s="11">
         <f>K7/1111</f>
         <v>0.96849684968496852</v>
       </c>
-      <c r="R7" s="17">
+      <c r="R7" s="11">
         <f>L7/33</f>
         <v>0.42424242424242425</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="G8" s="1"/>
       <c r="J8" s="1"/>
-      <c r="M8" s="25"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="25"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="16"/>
-    </row>
-    <row r="9">
+      <c r="M8" s="19"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -2166,6 +1977,12 @@
       <c r="D9">
         <v>1144</v>
       </c>
+      <c r="E9">
+        <v>1111</v>
+      </c>
+      <c r="F9">
+        <v>33</v>
+      </c>
       <c r="G9" s="1">
         <v>1294</v>
       </c>
@@ -2184,62 +2001,62 @@
       <c r="L9">
         <v>22</v>
       </c>
-      <c r="M9" s="25" t="s">
+      <c r="M9" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="N9" s="17">
+      <c r="N9" s="11">
         <f>K9/H9</f>
         <v>0.968476357267951</v>
       </c>
-      <c r="O9" s="17">
+      <c r="O9" s="11">
         <f>L9/I9</f>
         <v>0.14473684210526316</v>
       </c>
-      <c r="P9" s="25" t="s">
+      <c r="P9" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="Q9" s="17">
+      <c r="Q9" s="11">
         <f>K9/1111</f>
         <v>0.99549954995499546</v>
       </c>
-      <c r="R9" s="17">
+      <c r="R9" s="11">
         <f>L9/33</f>
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="G10" s="1"/>
       <c r="J10" s="1"/>
-      <c r="M10" s="22"/>
-      <c r="P10" s="22"/>
-    </row>
-    <row r="11">
+      <c r="M10" s="16"/>
+      <c r="P10" s="16"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="G11" s="1"/>
       <c r="J11" s="1"/>
-      <c r="M11" s="22"/>
-      <c r="P11" s="22"/>
-    </row>
-    <row r="12" ht="25.949999999999999" customHeight="1">
-      <c r="A12" s="13" t="s">
+      <c r="M11" s="16"/>
+      <c r="P11" s="16"/>
+    </row>
+    <row r="12" spans="1:18" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="13"/>
-    </row>
-    <row r="13">
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -2252,6 +2069,12 @@
       <c r="D13">
         <v>2355</v>
       </c>
+      <c r="E13">
+        <v>2326</v>
+      </c>
+      <c r="F13">
+        <v>29</v>
+      </c>
       <c r="G13" s="1">
         <v>2278</v>
       </c>
@@ -2270,40 +2093,40 @@
       <c r="L13">
         <v>9</v>
       </c>
-      <c r="M13" s="25" t="s">
+      <c r="M13" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="N13" s="17">
+      <c r="N13" s="11">
         <f>K13/H13</f>
         <v>0.99445471349353054</v>
       </c>
-      <c r="O13" s="17">
+      <c r="O13" s="11">
         <f>L13/I13</f>
-        <v>0.078947368421052627</v>
-      </c>
-      <c r="P13" s="25" t="s">
+        <v>7.8947368421052627E-2</v>
+      </c>
+      <c r="P13" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="Q13" s="17">
+      <c r="Q13" s="11">
         <f>K13/2326</f>
         <v>0.92519346517626833</v>
       </c>
-      <c r="R13" s="17">
+      <c r="R13" s="11">
         <f>L13/29</f>
         <v>0.31034482758620691</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="G14" s="1"/>
       <c r="J14" s="1"/>
-      <c r="M14" s="25"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
-      <c r="P14" s="25"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-    </row>
-    <row r="15">
+      <c r="M14" s="19"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -2316,6 +2139,12 @@
       <c r="D15">
         <v>2355</v>
       </c>
+      <c r="E15">
+        <v>2326</v>
+      </c>
+      <c r="F15">
+        <v>29</v>
+      </c>
       <c r="G15">
         <v>2505</v>
       </c>
@@ -2334,40 +2163,40 @@
       <c r="L15">
         <v>20</v>
       </c>
-      <c r="M15" s="25" t="s">
+      <c r="M15" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="N15" s="17">
+      <c r="N15" s="11">
         <f>K15/H15</f>
         <v>0.98208191126279865</v>
       </c>
-      <c r="O15" s="17">
+      <c r="O15" s="11">
         <f>L15/I15</f>
         <v>0.12422360248447205</v>
       </c>
-      <c r="P15" s="25" t="s">
+      <c r="P15" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="Q15" s="17">
+      <c r="Q15" s="11">
         <f>K15/2326</f>
         <v>0.98968185726569213</v>
       </c>
-      <c r="R15" s="17">
+      <c r="R15" s="11">
         <f>L15/29</f>
         <v>0.68965517241379315</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="G16" s="1"/>
       <c r="J16" s="1"/>
-      <c r="M16" s="25"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="25"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="16"/>
-    </row>
-    <row r="17">
+      <c r="M16" s="19"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="19"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -2380,6 +2209,12 @@
       <c r="D17">
         <v>2355</v>
       </c>
+      <c r="E17">
+        <v>2326</v>
+      </c>
+      <c r="F17">
+        <v>29</v>
+      </c>
       <c r="G17" s="1">
         <v>2317</v>
       </c>
@@ -2398,36 +2233,36 @@
       <c r="L17">
         <v>10</v>
       </c>
-      <c r="M17" s="25" t="s">
+      <c r="M17" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="N17" s="17">
+      <c r="N17" s="11">
         <f>K17/H17</f>
         <v>0.99225865209471764</v>
       </c>
-      <c r="O17" s="17">
+      <c r="O17" s="11">
         <f>L17/I17</f>
-        <v>0.082644628099173556</v>
-      </c>
-      <c r="P17" s="25" t="s">
+        <v>8.2644628099173556E-2</v>
+      </c>
+      <c r="P17" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="Q17" s="17">
+      <c r="Q17" s="11">
         <f>K17/2326</f>
         <v>0.93680137575236455</v>
       </c>
-      <c r="R17" s="17">
+      <c r="R17" s="11">
         <f>L17/29</f>
         <v>0.34482758620689657</v>
       </c>
     </row>
-    <row r="21" ht="14.25">
-      <c r="A21" s="18" t="s">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A21" s="12" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="22" ht="14.25">
-      <c r="A22" s="18" t="s">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A22" s="12" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2438,9 +2273,7 @@
     <mergeCell ref="A4:P4"/>
     <mergeCell ref="A12:P12"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/EX1/CP_res/EX1_CPa_effectivenes_all models.xlsx
+++ b/EX1/CP_res/EX1_CPa_effectivenes_all models.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xhulj\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xhulj\Desktop\CPa\EX1\CP_res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2847C6DD-99B5-4AD3-890F-BFF69D8AA68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700CA4F0-0D93-48F7-AF57-0B386B0FB717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="16080" windowWidth="29040" windowHeight="7965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LApredict" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="33">
   <si>
     <t>Correct predictions made by Lapredict</t>
   </si>
@@ -106,94 +106,28 @@
     <t>Test avg</t>
   </si>
   <si>
-    <t>0.91</t>
-  </si>
-  <si>
-    <t>0.45</t>
-  </si>
-  <si>
     <t>0.9</t>
   </si>
   <si>
     <t>Test AVG</t>
   </si>
   <si>
-    <t>0.89</t>
-  </si>
-  <si>
-    <t>0.67</t>
-  </si>
-  <si>
     <t>0.85</t>
   </si>
   <si>
-    <t>0.86</t>
-  </si>
-  <si>
-    <t>0.82</t>
-  </si>
-  <si>
     <t xml:space="preserve">QT </t>
   </si>
   <si>
-    <t>0.60</t>
-  </si>
-  <si>
-    <t>0.88</t>
-  </si>
-  <si>
-    <t>0.87</t>
-  </si>
-  <si>
-    <t>0.99</t>
-  </si>
-  <si>
     <t>LApredict with Openstack makes 3707 correct predictions; 3506 clean and 201 fault-prone</t>
   </si>
   <si>
     <t>LApredict with QT makes 4088 correct predictions; 4063 clean and 25 fault-prone</t>
   </si>
   <si>
-    <t>0.77</t>
-  </si>
-  <si>
-    <t>0.76</t>
-  </si>
-  <si>
-    <t>0.70</t>
-  </si>
-  <si>
-    <t>0.81</t>
-  </si>
-  <si>
-    <t>0.31</t>
-  </si>
-  <si>
-    <t>0.80</t>
-  </si>
-  <si>
-    <t>0.59</t>
-  </si>
-  <si>
-    <t>0.78</t>
-  </si>
-  <si>
     <t>DeepJIT with Openstack makes 777 correct predictions; 639 clean and 138 fault-prone</t>
   </si>
   <si>
     <t>DeepJIT with QT makes 1851 correct predictions; 1727 clean and 124 fault-prone</t>
-  </si>
-  <si>
-    <t>0.93</t>
-  </si>
-  <si>
-    <t>0.79</t>
-  </si>
-  <si>
-    <t>0.92</t>
-  </si>
-  <si>
-    <t>0.94</t>
   </si>
   <si>
     <t>CodeBERT4JIT with openstack makes 1144 correct predictions, where 1111 are clean and 33 fault prone</t>
@@ -217,39 +151,46 @@
       <sz val="11"/>
       <color theme="9"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="9"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="8" tint="0.39997558519241921"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF7030A0"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="8" tint="-0.249977111117893"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -764,8 +705,8 @@
       <c r="L5">
         <v>33</v>
       </c>
-      <c r="M5" s="10" t="s">
-        <v>23</v>
+      <c r="M5" s="10">
+        <v>0.91</v>
       </c>
       <c r="N5" s="11">
         <f>K5/H5</f>
@@ -775,8 +716,8 @@
         <f>L5/I5</f>
         <v>0.18032786885245902</v>
       </c>
-      <c r="P5" s="10" t="s">
-        <v>24</v>
+      <c r="P5" s="10">
+        <v>0.45</v>
       </c>
       <c r="Q5" s="11">
         <f>K5/3506</f>
@@ -795,10 +736,10 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C7">
         <v>4552</v>
@@ -830,8 +771,8 @@
       <c r="L7">
         <v>52</v>
       </c>
-      <c r="M7" s="10" t="s">
-        <v>27</v>
+      <c r="M7" s="10">
+        <v>0.89</v>
       </c>
       <c r="N7" s="11">
         <f>K7/H7</f>
@@ -841,8 +782,8 @@
         <f>L7/I7</f>
         <v>0.15522388059701492</v>
       </c>
-      <c r="P7" s="10" t="s">
-        <v>28</v>
+      <c r="P7" s="10">
+        <v>0.67</v>
       </c>
       <c r="Q7" s="11">
         <f>K7/3506</f>
@@ -861,7 +802,7 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
@@ -896,8 +837,8 @@
       <c r="L9">
         <v>92</v>
       </c>
-      <c r="M9" s="10" t="s">
-        <v>30</v>
+      <c r="M9" s="10">
+        <v>0.86</v>
       </c>
       <c r="N9" s="11">
         <f>K9/H9</f>
@@ -907,8 +848,8 @@
         <f>L9/I9</f>
         <v>0.17457305502846299</v>
       </c>
-      <c r="P9" s="10" t="s">
-        <v>31</v>
+      <c r="P9" s="10">
+        <v>0.82</v>
       </c>
       <c r="Q9" s="11">
         <f>K9/3506</f>
@@ -921,7 +862,7 @@
     </row>
     <row r="12" spans="1:18" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="23" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
@@ -976,8 +917,8 @@
       <c r="L13">
         <v>1</v>
       </c>
-      <c r="M13" s="10" t="s">
-        <v>23</v>
+      <c r="M13" s="10">
+        <v>0.91</v>
       </c>
       <c r="N13" s="11">
         <f>K13/H13</f>
@@ -987,8 +928,8 @@
         <f>L13/I13</f>
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="P13" s="10" t="s">
-        <v>33</v>
+      <c r="P13" s="10">
+        <v>0.6</v>
       </c>
       <c r="Q13" s="11">
         <f>K13/4063</f>
@@ -1005,7 +946,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
@@ -1040,8 +981,8 @@
       <c r="L15">
         <v>5</v>
       </c>
-      <c r="M15" s="10" t="s">
-        <v>34</v>
+      <c r="M15" s="10">
+        <v>0.88</v>
       </c>
       <c r="N15" s="11">
         <f>K15/H15</f>
@@ -1051,8 +992,8 @@
         <f>L15/I15</f>
         <v>1.0183299389002037E-2</v>
       </c>
-      <c r="P15" s="10" t="s">
-        <v>35</v>
+      <c r="P15" s="10">
+        <v>0.87</v>
       </c>
       <c r="Q15" s="11">
         <f>K15/4063</f>
@@ -1069,7 +1010,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
@@ -1104,8 +1045,8 @@
       <c r="L17">
         <v>15</v>
       </c>
-      <c r="M17" s="10" t="s">
-        <v>30</v>
+      <c r="M17" s="10">
+        <v>0.86</v>
       </c>
       <c r="N17" s="11">
         <f>K17/H17</f>
@@ -1115,8 +1056,8 @@
         <f>L17/I17</f>
         <v>2.2488755622188907E-2</v>
       </c>
-      <c r="P17" s="10" t="s">
-        <v>36</v>
+      <c r="P17" s="10">
+        <v>0.99</v>
       </c>
       <c r="Q17" s="11">
         <f>K17/4063</f>
@@ -1129,12 +1070,12 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1281,45 +1222,45 @@
         <v>138</v>
       </c>
       <c r="G5" s="1">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="H5">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="I5">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J5" s="1">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="K5">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="L5">
-        <v>25</v>
-      </c>
-      <c r="M5" s="10" t="s">
-        <v>39</v>
+        <v>27</v>
+      </c>
+      <c r="M5" s="10">
+        <v>0.77</v>
       </c>
       <c r="N5" s="11">
         <f>K5/H5</f>
-        <v>0.77910447761194035</v>
+        <v>0.7847025495750708</v>
       </c>
       <c r="O5" s="11">
         <f>L5/I5</f>
-        <v>0.86206896551724133</v>
+        <v>0.87096774193548387</v>
       </c>
       <c r="P5" s="10">
         <f>J5/777</f>
-        <v>0.36808236808236811</v>
+        <v>0.38996138996138996</v>
       </c>
       <c r="Q5" s="11">
         <f>K5/639</f>
-        <v>0.40845070422535212</v>
+        <v>0.43348982785602502</v>
       </c>
       <c r="R5" s="11">
         <f>L5/138</f>
-        <v>0.18115942028985507</v>
+        <v>0.19565217391304349</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -1333,10 +1274,10 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C7">
         <v>1331</v>
@@ -1363,21 +1304,21 @@
         <v>471</v>
       </c>
       <c r="K7">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L7">
-        <v>50</v>
-      </c>
-      <c r="M7" s="10" t="s">
-        <v>40</v>
+        <v>51</v>
+      </c>
+      <c r="M7" s="10">
+        <v>0.76</v>
       </c>
       <c r="N7" s="11">
         <f>K7/H7</f>
-        <v>0.7571942446043165</v>
+        <v>0.75539568345323738</v>
       </c>
       <c r="O7" s="11">
         <f>L7/I7</f>
-        <v>0.84745762711864403</v>
+        <v>0.86440677966101698</v>
       </c>
       <c r="P7" s="10">
         <f>J7/777</f>
@@ -1385,11 +1326,11 @@
       </c>
       <c r="Q7" s="11">
         <f>K7/639</f>
-        <v>0.65884194053208134</v>
+        <v>0.65727699530516437</v>
       </c>
       <c r="R7" s="11">
         <f>L7/138</f>
-        <v>0.36231884057971014</v>
+        <v>0.36956521739130432</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
@@ -1403,7 +1344,7 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
@@ -1424,10 +1365,10 @@
         <v>730</v>
       </c>
       <c r="H9">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="I9">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J9" s="1">
         <v>511</v>
@@ -1436,18 +1377,18 @@
         <v>438</v>
       </c>
       <c r="L9">
-        <v>72</v>
-      </c>
-      <c r="M9" s="10" t="s">
-        <v>41</v>
+        <v>73</v>
+      </c>
+      <c r="M9" s="10">
+        <v>0.7</v>
       </c>
       <c r="N9" s="11">
         <f>K9/H9</f>
-        <v>0.67592592592592593</v>
+        <v>0.67488443759630201</v>
       </c>
       <c r="O9" s="11">
         <f>L9/I9</f>
-        <v>0.87804878048780488</v>
+        <v>0.90123456790123457</v>
       </c>
       <c r="P9" s="10">
         <f>J9/777</f>
@@ -1459,7 +1400,7 @@
       </c>
       <c r="R9" s="11">
         <f>L9/138</f>
-        <v>0.52173913043478259</v>
+        <v>0.52898550724637683</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -1474,7 +1415,7 @@
     </row>
     <row r="12" spans="1:18" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="23" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
@@ -1524,32 +1465,32 @@
         <v>565</v>
       </c>
       <c r="K13">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="L13">
-        <v>42</v>
-      </c>
-      <c r="M13" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="M13" s="10">
+        <v>0.81</v>
       </c>
       <c r="N13" s="11">
         <f>K13/H13</f>
-        <v>0.81464174454828664</v>
+        <v>0.81308411214953269</v>
       </c>
       <c r="O13" s="11">
         <f>L13/I13</f>
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="P13" s="10" t="s">
-        <v>43</v>
+        <v>0.87755102040816324</v>
+      </c>
+      <c r="P13" s="10">
+        <v>0.31</v>
       </c>
       <c r="Q13" s="11">
         <f>K13/1727</f>
-        <v>0.30283729009843657</v>
+        <v>0.30225825130283729</v>
       </c>
       <c r="R13" s="11">
         <f>L13/124</f>
-        <v>0.33870967741935482</v>
+        <v>0.34677419354838712</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -1563,7 +1504,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
@@ -1598,8 +1539,8 @@
       <c r="L15">
         <v>72</v>
       </c>
-      <c r="M15" s="10" t="s">
-        <v>44</v>
+      <c r="M15" s="10">
+        <v>0.8</v>
       </c>
       <c r="N15" s="11">
         <f>K15/H15</f>
@@ -1609,8 +1550,8 @@
         <f>L15/I15</f>
         <v>0.77419354838709675</v>
       </c>
-      <c r="P15" s="10" t="s">
-        <v>45</v>
+      <c r="P15" s="10">
+        <v>0.59</v>
       </c>
       <c r="Q15" s="11">
         <f>K15/1727</f>
@@ -1632,7 +1573,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
@@ -1667,8 +1608,8 @@
       <c r="L17">
         <v>96</v>
       </c>
-      <c r="M17" s="10" t="s">
-        <v>46</v>
+      <c r="M17" s="10">
+        <v>0.78</v>
       </c>
       <c r="N17" s="11">
         <f>K17/H17</f>
@@ -1678,8 +1619,8 @@
         <f>L17/I17</f>
         <v>0.72180451127819545</v>
       </c>
-      <c r="P17" s="10" t="s">
-        <v>40</v>
+      <c r="P17" s="10">
+        <v>0.76</v>
       </c>
       <c r="Q17" s="11">
         <f>K17/1727</f>
@@ -1692,12 +1633,12 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1847,41 +1788,41 @@
         <v>967</v>
       </c>
       <c r="H5">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="I5">
-        <v>67</v>
-      </c>
-      <c r="J5">
+        <v>68</v>
+      </c>
+      <c r="J5" s="1">
         <v>899</v>
       </c>
       <c r="K5">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="L5">
-        <v>3</v>
-      </c>
-      <c r="M5" s="19" t="s">
-        <v>49</v>
+        <v>6</v>
+      </c>
+      <c r="M5" s="19">
+        <v>0.93</v>
       </c>
       <c r="N5" s="11">
         <f>K5/H5</f>
-        <v>0.99555555555555553</v>
+        <v>0.99332591768631817</v>
       </c>
       <c r="O5" s="11">
         <f>L5/I5</f>
-        <v>4.4776119402985072E-2</v>
-      </c>
-      <c r="P5" s="19" t="s">
-        <v>50</v>
+        <v>8.8235294117647065E-2</v>
+      </c>
+      <c r="P5" s="19">
+        <v>0.79</v>
       </c>
       <c r="Q5" s="11">
         <f>K5/1111</f>
-        <v>0.80648064806480646</v>
+        <v>0.80378037803780378</v>
       </c>
       <c r="R5" s="11">
         <f>L5/33</f>
-        <v>9.0909090909090912E-2</v>
+        <v>0.18181818181818182</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -1896,7 +1837,7 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
@@ -1931,8 +1872,8 @@
       <c r="L7">
         <v>14</v>
       </c>
-      <c r="M7" s="19" t="s">
-        <v>27</v>
+      <c r="M7" s="19">
+        <v>0.89</v>
       </c>
       <c r="N7" s="11">
         <f>K7/H7</f>
@@ -1942,8 +1883,8 @@
         <f>L7/I7</f>
         <v>0.1076923076923077</v>
       </c>
-      <c r="P7" s="19" t="s">
-        <v>21</v>
+      <c r="P7" s="19">
+        <v>0.95</v>
       </c>
       <c r="Q7" s="11">
         <f>K7/1111</f>
@@ -1966,7 +1907,7 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
@@ -1984,44 +1925,44 @@
         <v>33</v>
       </c>
       <c r="G9" s="1">
-        <v>1294</v>
+        <v>1297</v>
       </c>
       <c r="H9">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="I9">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J9" s="1">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="K9">
-        <v>1106</v>
+        <v>1101</v>
       </c>
       <c r="L9">
-        <v>22</v>
-      </c>
-      <c r="M9" s="19" t="s">
-        <v>35</v>
+        <v>25</v>
+      </c>
+      <c r="M9" s="19">
+        <v>0.87</v>
       </c>
       <c r="N9" s="11">
         <f>K9/H9</f>
-        <v>0.968476357267951</v>
+        <v>0.96241258741258739</v>
       </c>
       <c r="O9" s="11">
         <f>L9/I9</f>
-        <v>0.14473684210526316</v>
-      </c>
-      <c r="P9" s="19" t="s">
-        <v>36</v>
+        <v>0.16339869281045752</v>
+      </c>
+      <c r="P9" s="19">
+        <v>0.98</v>
       </c>
       <c r="Q9" s="11">
         <f>K9/1111</f>
-        <v>0.99549954995499546</v>
+        <v>0.99099909990999102</v>
       </c>
       <c r="R9" s="11">
         <f>L9/33</f>
-        <v>0.66666666666666663</v>
+        <v>0.75757575757575757</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -2038,7 +1979,7 @@
     </row>
     <row r="12" spans="1:18" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="23" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
@@ -2076,44 +2017,44 @@
         <v>29</v>
       </c>
       <c r="G13" s="1">
-        <v>2278</v>
+        <v>2269</v>
       </c>
       <c r="H13">
-        <v>2164</v>
+        <v>2153</v>
       </c>
       <c r="I13">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J13" s="1">
-        <v>2161</v>
+        <v>2150</v>
       </c>
       <c r="K13">
-        <v>2152</v>
+        <v>2140</v>
       </c>
       <c r="L13">
-        <v>9</v>
-      </c>
-      <c r="M13" s="19" t="s">
-        <v>21</v>
+        <v>10</v>
+      </c>
+      <c r="M13" s="19">
+        <v>0.95</v>
       </c>
       <c r="N13" s="11">
         <f>K13/H13</f>
-        <v>0.99445471349353054</v>
+        <v>0.99396191360891784</v>
       </c>
       <c r="O13" s="11">
         <f>L13/I13</f>
-        <v>7.8947368421052627E-2</v>
-      </c>
-      <c r="P13" s="19" t="s">
-        <v>51</v>
+        <v>8.6206896551724144E-2</v>
+      </c>
+      <c r="P13" s="19">
+        <v>0.91</v>
       </c>
       <c r="Q13" s="11">
         <f>K13/2326</f>
-        <v>0.92519346517626833</v>
+        <v>0.92003439380911434</v>
       </c>
       <c r="R13" s="11">
         <f>L13/29</f>
-        <v>0.31034482758620691</v>
+        <v>0.34482758620689657</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -2128,7 +2069,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
@@ -2145,7 +2086,7 @@
       <c r="F15">
         <v>29</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>2505</v>
       </c>
       <c r="H15">
@@ -2155,35 +2096,35 @@
         <v>161</v>
       </c>
       <c r="J15" s="1">
-        <v>2322</v>
+        <v>2320</v>
       </c>
       <c r="K15">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="L15">
-        <v>20</v>
-      </c>
-      <c r="M15" s="19" t="s">
-        <v>49</v>
+        <v>21</v>
+      </c>
+      <c r="M15" s="19">
+        <v>0.93</v>
       </c>
       <c r="N15" s="11">
         <f>K15/H15</f>
-        <v>0.98208191126279865</v>
+        <v>0.98080204778156999</v>
       </c>
       <c r="O15" s="11">
         <f>L15/I15</f>
-        <v>0.12422360248447205</v>
-      </c>
-      <c r="P15" s="19" t="s">
-        <v>36</v>
+        <v>0.13043478260869565</v>
+      </c>
+      <c r="P15" s="19">
+        <v>0.99</v>
       </c>
       <c r="Q15" s="11">
         <f>K15/2326</f>
-        <v>0.98968185726569213</v>
+        <v>0.98839208942390366</v>
       </c>
       <c r="R15" s="11">
         <f>L15/29</f>
-        <v>0.68965517241379315</v>
+        <v>0.72413793103448276</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
@@ -2198,7 +2139,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
@@ -2216,54 +2157,54 @@
         <v>29</v>
       </c>
       <c r="G17" s="1">
-        <v>2317</v>
+        <v>2313</v>
       </c>
       <c r="H17">
-        <v>2196</v>
+        <v>2191</v>
       </c>
       <c r="I17">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J17" s="1">
-        <v>2189</v>
+        <v>2184</v>
       </c>
       <c r="K17">
-        <v>2179</v>
+        <v>2173</v>
       </c>
       <c r="L17">
-        <v>10</v>
-      </c>
-      <c r="M17" s="19" t="s">
-        <v>52</v>
+        <v>11</v>
+      </c>
+      <c r="M17" s="19">
+        <v>0.94</v>
       </c>
       <c r="N17" s="11">
         <f>K17/H17</f>
-        <v>0.99225865209471764</v>
+        <v>0.99178457325422187</v>
       </c>
       <c r="O17" s="11">
         <f>L17/I17</f>
-        <v>8.2644628099173556E-2</v>
-      </c>
-      <c r="P17" s="19" t="s">
-        <v>49</v>
+        <v>9.0163934426229511E-2</v>
+      </c>
+      <c r="P17" s="19">
+        <v>0.93</v>
       </c>
       <c r="Q17" s="11">
         <f>K17/2326</f>
-        <v>0.93680137575236455</v>
+        <v>0.93422184006878761</v>
       </c>
       <c r="R17" s="11">
         <f>L17/29</f>
-        <v>0.34482758620689657</v>
+        <v>0.37931034482758619</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
